--- a/data/current_technologies.xlsx
+++ b/data/current_technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF6508D-278C-43B9-9B79-0A4AA57C7E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3E58D4-DADF-457F-97C3-7D2607A4D865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-375" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>

--- a/data/current_technologies.xlsx
+++ b/data/current_technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3E58D4-DADF-457F-97C3-7D2607A4D865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D473AC7-F228-4D69-AB32-388F56B3130D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
   <si>
     <t>BEL1</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>NL4</t>
+  </si>
+  <si>
+    <t>SMR</t>
   </si>
 </sst>
 </file>
@@ -404,10 +407,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -429,8 +435,11 @@
       <c r="H1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -450,7 +459,7 @@
         <v>946.40817160641484</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -470,7 +479,7 @@
         <v>822.6725536812711</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -478,7 +487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -486,12 +495,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -499,7 +508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -507,7 +516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -523,7 +532,7 @@
         <v>45.662100456621005</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -531,12 +540,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -556,7 +565,7 @@
         <v>443.89055836407067</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -576,7 +585,7 @@
         <v>515.11377787841059</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -592,7 +601,7 @@
         <v>39.954337899543376</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -607,23 +616,27 @@
         <f>C17/0.823</f>
         <v>38.837752514744473</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17">
+        <f>H17/2.125</f>
+        <v>18.276589418703281</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -639,17 +652,17 @@
         <v>216.89497716894977</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1</v>
       </c>
@@ -669,7 +682,7 @@
         <v>565.33231489763716</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>2</v>
       </c>
@@ -689,37 +702,37 @@
         <v>471.71591380806819</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -734,13 +747,17 @@
         <f>C35/0.823</f>
         <v>117.90032013404574</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35">
+        <f>H35/2.125</f>
+        <v>55.482503592492115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1</v>
       </c>
@@ -760,7 +777,7 @@
         <v>328.69164874146196</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>2</v>
       </c>
@@ -780,12 +797,12 @@
         <v>328.69164874146196</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>

--- a/data/current_technologies.xlsx
+++ b/data/current_technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D473AC7-F228-4D69-AB32-388F56B3130D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71663D3-CEC0-46FC-9386-2B9CE26F03EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="19">
   <si>
     <t>BEL1</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>SMR</t>
+  </si>
+  <si>
+    <t>WGS_syngas</t>
   </si>
 </sst>
 </file>
@@ -407,13 +410,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -438,8 +442,11 @@
       <c r="I1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -459,7 +466,7 @@
         <v>946.40817160641484</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -479,7 +486,7 @@
         <v>822.6725536812711</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -487,7 +494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -495,12 +502,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -508,7 +515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -516,7 +523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -531,8 +538,16 @@
         <f>C10</f>
         <v>45.662100456621005</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I10">
+        <f>G10*0.3544</f>
+        <v>16.182648401826484</v>
+      </c>
+      <c r="J10">
+        <f>G10*0.7532</f>
+        <v>34.392694063926939</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -540,12 +555,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -565,7 +580,7 @@
         <v>443.89055836407067</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -585,7 +600,7 @@
         <v>515.11377787841059</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -600,8 +615,16 @@
         <f>C16</f>
         <v>39.954337899543376</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I16">
+        <f>G16*0.3544</f>
+        <v>14.159817351598171</v>
+      </c>
+      <c r="J16">
+        <f>G16*0.7532</f>
+        <v>30.093607305936068</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -620,23 +643,27 @@
         <f>H17/2.125</f>
         <v>18.276589418703281</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17">
+        <f>I17*2.125</f>
+        <v>38.837752514744473</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -651,18 +678,26 @@
         <f>C22</f>
         <v>216.89497716894977</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I22">
+        <f>G22*0.3544</f>
+        <v>76.867579908675793</v>
+      </c>
+      <c r="J22">
+        <f>G22*0.7532</f>
+        <v>163.36529680365297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1</v>
       </c>
@@ -682,7 +717,7 @@
         <v>565.33231489763716</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>2</v>
       </c>
@@ -702,37 +737,37 @@
         <v>471.71591380806819</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -751,13 +786,17 @@
         <f>H35/2.125</f>
         <v>55.482503592492115</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35">
+        <f>I35*2.125</f>
+        <v>117.90032013404574</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1</v>
       </c>
@@ -769,40 +808,40 @@
         <v>89.041095890410958</v>
       </c>
       <c r="E38">
-        <f>E39</f>
-        <v>328.69164874146196</v>
+        <f>C38/0.1363</f>
+        <v>653.27289721504735</v>
       </c>
       <c r="F38">
-        <f>F39</f>
-        <v>328.69164874146196</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+        <f>E38</f>
+        <v>653.27289721504735</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>2</v>
       </c>
       <c r="B39">
-        <v>871</v>
+        <v>971</v>
       </c>
       <c r="C39">
         <f t="shared" ref="C39" si="2">B39*1000/8760</f>
-        <v>99.429223744292244</v>
+        <v>110.84474885844749</v>
       </c>
       <c r="E39">
         <f>C39/0.3025</f>
-        <v>328.69164874146196</v>
+        <v>366.42892184610741</v>
       </c>
       <c r="F39">
         <f>E39</f>
-        <v>328.69164874146196</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+        <v>366.42892184610741</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>
